--- a/experiment/task/instructions_strategy_up.xlsx
+++ b/experiment/task/instructions_strategy_up.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>instructionText</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>toldCorrect</t>
         </is>
       </c>
     </row>
@@ -432,6 +437,11 @@
 One way to increase the intensity of your emotional response is to watch each video as if you were there. Imagine the events unfolding right in front of you, and focus on what the people in the video are seeing, hearing and feeling.</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Improve</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
